--- a/kanteikyoku_stores_修正版.xlsx
+++ b/kanteikyoku_stores_修正版.xlsx
@@ -196,7 +196,7 @@
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>公式表記は「増田字柳田73-1」</t>
+        <t>公式表記「増田字柳田73-1」に修正済み（元は「増田柳田73-1」）</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
@@ -811,9 +811,9 @@
           <t>981-1224</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>宮城県名取市増田柳田73-1</t>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>宮城県名取市増田字柳田73-1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>[住所] 公式表記は「増田字柳田73-1」
+          <t>[住所] 公式表記「増田字柳田73-1」に修正済み（元は「増田柳田73-1」）
 [店舗形態] 直営店である根拠は未確認（推定）</t>
         </is>
       </c>
@@ -4781,7 +4781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4839,86 +4839,98 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>追加</t>
+          <t>修正</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>「注記（要確認事項）」列を追加</t>
+          <t>名取店の住所を公式表記「宮城県名取市増田字柳田73-1」に変更</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>再集計</t>
+          <t>追加</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>「フランチャイズ運営会社一覧」を削除後の店舗で再集計</t>
+          <t>「注記（要確認事項）」列を追加</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>再集計</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>「フランチャイズ運営会社一覧」を削除後の店舗で再集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>掲載店舗数 75 → 70（質屋かんてい局のみ）</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-    </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>凡例</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>黄色</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>要確認（情報源によって食い違い／裏付けが不十分）。セルにコメントあり</t>
-        </is>
-      </c>
+          <t>凡例</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>黄色</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>要確認（情報源によって食い違い／裏付けが不十分）。セルにコメントあり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>緑色</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>今回修正した箇所</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-    </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>公式サイトに直接アクセスできない環境のため、Web検索結果（公式店舗一覧・各店舗ページ・プレスリリース等）との照合による。2026年10月14日時点</t>
         </is>

--- a/kanteikyoku_stores_修正版.xlsx
+++ b/kanteikyoku_stores_修正版.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フランチャイズ運営会社一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更内容" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="買取専門店一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フランチャイズ運営会社一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更内容" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗一覧'!$A$1:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'買取専門店一覧'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -106,6 +108,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4335,442 +4346,333 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>運営会社名</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>店舗数</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>店舗名（都道府県）</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>店名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>営業時間</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>店舗ページURL</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>店舗形態</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>運営会社（フランチャイズの場合）</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>注記（要確認事項）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>株式会社デザート</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>新潟松崎店（新潟県）、新潟万代店（新潟県）、上越店（新潟県）、新潟桜木店（新潟県）、長岡店（新潟県）、新潟東店（新潟県）、新潟南店（新潟県）</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>大垣店</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>503-0864</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>岐阜県大垣市南頬町4丁目58-1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0584-74-7235</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-19:00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://kanteikyoku-web.jp/tenpo/ogaki/</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>直営店</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>株式会社栄商</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>宇都宮店（栃木県）、宇都宮戸祭店（栃木県）、那須塩原店（栃木県）、鹿沼店（栃木県）、小山店（栃木県）、上尾駅前店（埼玉県）</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>豊橋柱店</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>441-8059</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>愛知県豊橋市柱五番町116-1 フィールえくぼ店内</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0532-37-1222</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>10:00-13:00／14:00-20:00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://kanteikyoku.jp/store/toyohashihashira/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>フランチャイズ店</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>株式会社ティーバイティー</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>株式会社シンク</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>松山インター店（愛媛県）、松山朝生田店（愛媛県）、松前R56店（愛媛県）、松山久万ノ台店（愛媛県）、新居浜店（愛媛県）、西条店（愛媛県）</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>神戸玉津店</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>651-2143</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市西区丸塚2丁目9-18 ホームランスタジアム1階</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>078-922-1133</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>月火木(2・4・5週)・日10:00-18:00／金土祝前日10:00-19:00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://kanteikyoku.jp/store/tamatsu/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>フランチャイズ店</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>株式会社アルプス</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>株式会社ビッグジェイ</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>つかざん店（沖縄県）、小禄金城店（沖縄県）、コザ山内店（沖縄県）、那覇店（沖縄県）、宜野湾愛知店（沖縄県）、名護店（沖縄県）</t>
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>じゃんぼスクエア香芝店</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>639-0236</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>奈良県香芝市磯壁3丁目40-1 じゃんぼスクエア香芝内</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0120-56-6789</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10:00-19:00（最終受付18:30）</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://kanteikyoku.jp/store/kashiba/</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>直営店</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>[店舗形態] 直営店である根拠は未確認（推定）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>株式会社英和実業</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>光の森店（熊本県）、上水前寺店（熊本県）、南高江店（熊本県）、飛田店（熊本県）、南熊本店（熊本県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>株式会社エト・アール</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>仙台泉店（宮城県）、山形南店（山形県）、山形北店（山形県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>有限会社ブックスふかざわ</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>金沢福久店（石川県）、金沢バイパス店（石川県）、金沢久安店（石川県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>株式会社ブロードアイ</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>仙台卸町店（宮城県）、利府店（宮城県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>株式会社ライズコーポレーション</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>秋田店（秋田県）、亀有店（東京都）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>有限会社べルージュ</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>土浦店（茨城県）、つくば店（茨城県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>伯楽株式会社</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>松戸店（千葉県）、三軒茶屋店（伯楽）（東京都）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>株式会社ティーバイティー</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>名古屋栄錦三丁目店（愛知県）、名古屋緑店（愛知県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>株式会社オレンジライン</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>盛岡店（岩手県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>株式会社むさしの</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>前橋店（群馬県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>株式会社夢現</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>市川インター店（千葉県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>ハッピーアンドドリーム株式会社</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>富山インター店（富山県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>ECマーケット株式会社</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>松本店（長野県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>有限会社旅人／株式会社tabito</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>名古屋西店（愛知県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>龍玉精工株式会社</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>刈谷店（愛知県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>株式会社秀陽</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>名古屋東郷店（愛知県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>株式会社H3</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>四條畷店（大阪府）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>日本エスクローサービス株式会社／株式会社アールティ</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>伊丹店（兵庫県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>株式会社アルプス</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>神戸大蔵谷インター店（兵庫県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>株式会社フィールキャスト</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>加古川店（兵庫県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>株式会社ネオプラン</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>太宰府店（福岡県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>株式会社リバーサンド</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>美里店（沖縄県）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>FTC直営店（運営会社の記載なし・FTC株式会社による直営と推定）</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>八戸店（青森県）、名取店（宮城県）、須賀川店（福島県）、会津若松店（福島県）、横浜港南店（神奈川県）、茜部店（岐阜県）、細畑店（岐阜県）、春日井店（愛知県）、北名古屋店（愛知県）、小牧店（愛知県）</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>高知中久万店</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>780-0983</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>高知県高知市中久万238-4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>088-802-8661</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9:30-18:00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://kanteikyoku.jp/store/kochi/</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>直営店</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026年10月9日グランドオープン（PR TIMES）
+[店舗形態] 直営店である根拠は未確認（推定）</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4781,7 +4683,1017 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>運営会社名</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>店舗数</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>店舗名（都道府県）</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>備考（出典・確認状況）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>株式会社デザート</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>新潟松崎店（新潟県）、新潟万代店（新潟県）、上越店（新潟県）、新潟桜木店（新潟県）、長岡店（新潟県）、新潟東店（新潟県）、新潟南店（新潟県）</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>260-0015</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>千葉県千葉市中央区富士見2-13-1 第2山崎ビル2F</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>株式会社栄商</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>宇都宮店（栃木県）、宇都宮戸祭店（栃木県）、那須塩原店（栃木県）、鹿沼店（栃木県）、小山店（栃木県）、上尾駅前店（埼玉県）</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>321-0904</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>栃木県宇都宮市陽東2-8-12</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>住所:運営会社サイト(kanteikyoku.net/company)。ウリドキでは「宇都宮市平出町3743-6(〒321-0901)」と異なる表記あり。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>株式会社シンク</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>松山インター店（愛媛県）、松山朝生田店（愛媛県）、松前R56店（愛媛県）、松山久万ノ台店（愛媛県）、新居浜店（愛媛県）、西条店（愛媛県）</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>792-0801</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>愛媛県新居浜市菊本町1-1-30 2F</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>住所:運営会社サイト(kanteikyoku-shikoku.jp/company/)。郵便番号は住所から補完(ウリドキの「792-0000」は誤り)。サイト掲載の089-961-8878は松前R56店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>株式会社ビッグジェイ</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>つかざん店（沖縄県）、小禄金城店（沖縄県）、コザ山内店（沖縄県）、那覇店（沖縄県）、宜野湾愛知店（沖縄県）、名護店（沖縄県）</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>902-0061</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>沖縄県那覇市古島1-25-6</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>098-885-6200</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。電話は同住所の那覇店の番号(本社専用番号は未確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>株式会社英和実業</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>光の森店（熊本県）、上水前寺店（熊本県）、南高江店（熊本県）、飛田店（熊本県）、南熊本店（熊本県）</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>862-0942</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>熊本県熊本市東区江津2-37-1</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>株式会社エト・アール</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>仙台泉店（宮城県）、山形南店（山形県）、山形北店（山形県）</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>999-3115</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>山形県上山市高野64</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>有限会社ブックスふかざわ</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>金沢福久店（石川県）、金沢バイパス店（石川県）、金沢久安店（石川県）</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>924-0803</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>石川県白山市乾町117-1</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>076-274-7810</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(同住所の金沢バイパス店)。郵便番号はウリドキの921-8164(金沢市久安)が誤りのため住所から補完。電話は金沢バイパス店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>株式会社ブロードアイ</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>仙台卸町店（宮城県）、利府店（宮城県）</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>994-0047</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>山形県天童市駅西1-1-1</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>住所:七十七銀行ニュースリリース(2026年9月)・ウリドキで一致。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>株式会社ライズコーポレーション</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>秋田店（秋田県）、亀有店（東京都）</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>125-0061</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>東京都葛飾区亀有3-22-6</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>03-6240-7118</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>住所:運営会社サイト・ウリドキ(亀有店と同住所)。登記上の本店かは未確認。電話は亀有店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>有限会社べルージュ</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>土浦店（茨城県）、つくば店（茨城県）</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>305-0035</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>茨城県つくば市松代1-9-2</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>029-879-7700</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(つくば店と同住所)。電話はつくば店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>伯楽株式会社</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>松戸店（千葉県）、三軒茶屋店（伯楽）（東京都）</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>154-0024</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>東京都世田谷区三軒茶屋2-13-13</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>03-3410-1088</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(三軒茶屋店と同住所)。電話は三軒茶屋店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>株式会社ティーバイティー</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>名古屋栄錦三丁目店（愛知県）、名古屋緑店（愛知県）</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>470-1132</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>愛知県豊明市間米町敷田1225-12</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>0562-91-3396</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ・プレスリリース(value-press)で一致。電話はプレスリリース(2015年)掲載の番号のため変更の可能性あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>株式会社オレンジライン</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>盛岡店（岩手県）</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>020-0866</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>岩手県盛岡市本宮6-32-30</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>019-601-3171</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(盛岡店と同住所)。電話は盛岡店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>株式会社むさしの</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>前橋店（群馬県）</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>368-0005</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>埼玉県秩父市大野原567</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。法人情報サイトに同住所の「株式会社むさしの」が吸収合併で閉鎖との記載あり。現在の状況は要確認。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>株式会社夢現</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>市川インター店（千葉県）</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>272-0026</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>千葉県市川市東大和田1-26-19</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>047-711-2663</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(市川インター店と同住所)。電話は市川インター店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ハッピーアンドドリーム株式会社</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>富山インター店（富山県）</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>930-0864</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>富山県富山市羽根80-1</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>076-495-6611</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>住所:採用サイト(en-gage)。電話:マイナビ掲載の同住所の本社電話。社名との対応が明記されていないため要確認。郵便番号は住所から補完</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ECマーケット株式会社</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>松本店（長野県）</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>396-0013</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>長野県伊那市下新田3023</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>有限会社旅人／株式会社tabito</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>名古屋西店（愛知県）</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>451-0043</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>愛知県名古屋市西区新道1-1-1 SS23ビル1F</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>052-583-0055</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(有限会社旅人として掲載。名古屋西店と同住所)。電話は名古屋西店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>龍玉精工株式会社</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>刈谷店（愛知県）</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>444-2135</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>愛知県岡崎市大門1-5-15</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。地図サイトでは同住所は「龍玉精工 住建営業部」。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>株式会社秀陽</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>名古屋東郷店（愛知県）</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>470-0152</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>愛知県愛知郡東郷町北山台3-5-1</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>0561-39-4178</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(名古屋東郷店と同住所)。電話は名古屋東郷店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>株式会社H3</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>四條畷店（大阪府）</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>595-0055</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>大阪府泉大津市なぎさ町6-1 きららセンタービル12階</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>日本エスクローサービス株式会社／株式会社アールティ</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>伊丹店（兵庫県）</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>650-0012</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市中央区北長狭通4-4-18 富士信ビル3F</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(日本エスクローサービス株式会社)。株式会社アールティの所在地は未確認。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>株式会社アルプス</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>神戸大蔵谷インター店（兵庫県）</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>652-0801</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市兵庫区中道通7-1-7</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>株式会社フィールキャスト</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>加古川店（兵庫県）</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>675-0113</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>兵庫県加古川市平岡町中野774-1</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>079-430-6688</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(加古川店と同住所)。電話は加古川店の番号</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>株式会社ネオプラン</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>太宰府店（福岡県）</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>818-0132</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>福岡県太宰府市国分3-10-1</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>0120-074-080</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地(太宰府店と同住所)。電話は太宰府店のフリーダイヤル</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>株式会社リバーサンド</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>美里店（沖縄県）</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>904-2155</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>沖縄県沖縄市美原2-16-24</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>住所:ウリドキ店舗ページの運営会社所在地。本社電話は見つからず</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>FTC直営店（運営会社の記載なし・FTC株式会社による直営と推定）</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>八戸店（青森県）、名取店（宮城県）、須賀川店（福島県）、会津若松店（福島県）、横浜港南店（神奈川県）、茜部店（岐阜県）、細畑店（岐阜県）、春日井店（愛知県）、北名古屋店（愛知県）、小牧店（愛知県）</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>503-0023</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>岐阜県大垣市笠木町260-1</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>0584-92-1222</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>FTC株式会社(かんてい局本部)の本社。住所・電話:FTC公式サイト(ftcproject.co.jp/company/)の代表番号</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4936,6 +5848,54 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>「フランチャイズ運営会社一覧」に郵便番号・住所・電話番号・備考の4列を追加（全27社＋FTC本部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>電話番号は本社専用の番号がほとんど公開されておらず、本社と同じ住所の店舗の番号を入れた会社があります（備考に記載）。見つからない会社は「未確認」</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>気づいた点</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>ウリドキでは名取店・須賀川店・会津若松店の運営会社が「株式会社ケービーディージャパン（福島県郡山市南1-35）」、横浜港南店が「株式会社テルトル・ルージュ」、小禄金城店が「FTC株式会社」と掲載。店舗一覧シートの区分（FTC直営推定／ビッグジェイ）と食い違うため要確認（店舗一覧シートは未変更）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>確認方法</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>運営会社サイト・FTC公式サイト・ウリドキ店舗ページ・金融機関/企業プレスリリース・採用サイトを照合。郵便番号は日本郵便データ（zipcloud）で住所と照合。2026年10月14日時点</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
